--- a/contracts/0x0aBCFbfA8e3Fda8B7FBA18721Caf7d5cf55cF5f5/output_debug/events.xlsx
+++ b/contracts/0x0aBCFbfA8e3Fda8B7FBA18721Caf7d5cf55cF5f5/output_debug/events.xlsx
@@ -483,7 +483,11 @@
           <t>0x5d0634fe981be85c22e2942a880821b70095d84e152c3ea3c17a4e4250d9d61</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LogSwapin(bytes32,address,uint256)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>0xa06</t>
